--- a/reports/Debug-snowbowl-20251230/For The Week Ending (Prior Year)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20251230/For The Week Ending (Prior Year)_Visits.xlsx
@@ -31,16 +31,16 @@
     <t>Location</t>
   </si>
   <si>
+    <t>Snowbowl Comp Tickets</t>
+  </si>
+  <si>
     <t>Snowbowl Passes</t>
   </si>
   <si>
+    <t>Snowbowl Tickets</t>
+  </si>
+  <si>
     <t>Snowbowl Uplift Tickets</t>
-  </si>
-  <si>
-    <t>Snowbowl Comp Tickets</t>
-  </si>
-  <si>
-    <t>Snowbowl Tickets</t>
   </si>
 </sst>
 </file>
@@ -431,10 +431,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>45657</v>
+        <v>45656</v>
       </c>
       <c r="C2" s="2">
-        <v>3</v>
+        <v>546</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -445,10 +445,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>45657</v>
+        <v>45656</v>
       </c>
       <c r="C3" s="2">
-        <v>266</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -462,10 +462,10 @@
         <v>45656</v>
       </c>
       <c r="C4" s="2">
-        <v>546</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -473,13 +473,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="C5" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,10 +490,10 @@
         <v>45656</v>
       </c>
       <c r="C6" s="2">
-        <v>2</v>
+        <v>633</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,7 +504,7 @@
         <v>45657</v>
       </c>
       <c r="C7" s="2">
-        <v>8</v>
+        <v>490</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -518,10 +518,10 @@
         <v>45656</v>
       </c>
       <c r="C8" s="2">
-        <v>633</v>
+        <v>1705</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -532,10 +532,10 @@
         <v>45657</v>
       </c>
       <c r="C9" s="2">
-        <v>490</v>
+        <v>3</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,10 +546,10 @@
         <v>45656</v>
       </c>
       <c r="C10" s="2">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -557,10 +557,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>45657</v>
+        <v>45656</v>
       </c>
       <c r="C11" s="2">
-        <v>1496</v>
+        <v>272</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>8</v>
@@ -571,13 +571,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="C12" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -585,10 +585,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="C13" s="2">
-        <v>272</v>
+        <v>58</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>6</v>
@@ -602,10 +602,10 @@
         <v>45657</v>
       </c>
       <c r="C14" s="2">
-        <v>1</v>
+        <v>471</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -616,10 +616,10 @@
         <v>45657</v>
       </c>
       <c r="C15" s="2">
-        <v>58</v>
+        <v>266</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -627,13 +627,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>45657</v>
+        <v>45656</v>
       </c>
       <c r="C16" s="2">
-        <v>471</v>
+        <v>48</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -641,13 +641,13 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>45656</v>
+        <v>45657</v>
       </c>
       <c r="C17" s="2">
-        <v>1705</v>
+        <v>1496</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
